--- a/templates/offer_template.xlsx
+++ b/templates/offer_template.xlsx
@@ -226,7 +226,7 @@
     <numFmt numFmtId="170" formatCode="#,##0&quot; €&quot;;[RED]\-#,##0&quot; €&quot;"/>
     <numFmt numFmtId="171" formatCode="_-* #,##0.00&quot; €&quot;_-;\-* #,##0.00&quot; €&quot;_-;_-* \-??&quot; €&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -362,10 +362,22 @@
       <family val="0"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="0"/>
+    </font>
+    <font>
       <u val="single"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
       <family val="0"/>
     </font>
     <font>
@@ -395,6 +407,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -522,40 +541,44 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="83">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -563,59 +586,59 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -631,7 +654,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -639,171 +662,171 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -815,7 +838,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -823,17 +846,29 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -924,9 +959,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>704520</xdr:colOff>
+      <xdr:colOff>704160</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>185400</xdr:rowOff>
+      <xdr:rowOff>185040</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -935,8 +970,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5563440" y="1796760"/>
-          <a:ext cx="2216160" cy="1058040"/>
+          <a:off x="5562720" y="1796760"/>
+          <a:ext cx="2215800" cy="1057680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1080,13 +1115,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>95400</xdr:colOff>
       <xdr:row>69</xdr:row>
-      <xdr:rowOff>128160</xdr:rowOff>
+      <xdr:rowOff>146160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>15120</xdr:colOff>
-      <xdr:row>121</xdr:row>
-      <xdr:rowOff>180360</xdr:rowOff>
+      <xdr:colOff>14760</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>44640</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1096,7 +1131,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="95400" y="13700160"/>
-          <a:ext cx="5714640" cy="9957960"/>
+          <a:ext cx="5713560" cy="9042480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1775,7 +1810,7 @@
               <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
-            <a:t>______________________                                                        _________________________</a:t>
+            <a:t>_________________________                                   _______________________________________</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="de-DE" sz="1100" b="0" u="none" strike="noStrike">
@@ -1804,17 +1839,17 @@
             </a:tabLst>
           </a:pPr>
           <a:r>
-            <a:rPr lang="de-DE" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" u="none" strike="noStrike">
+            <a:rPr lang="de-DE" sz="900" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Datum, Unterschrift Kunde                                          Datum, Unterschrift Umzugsunternehmen</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="900" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -1830,17 +1865,28 @@
             </a:tabLst>
           </a:pPr>
           <a:r>
-            <a:rPr lang="de-DE" sz="900" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>Datum, Unterschrift Kunde                                                                               Datum, Unterschrift Umzugsunternehmen</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="900" b="0" u="none" strike="noStrike">
+            <a:rPr lang="de-DE" sz="1100" b="1" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:t>___________________________________________________________________________</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="de-DE" sz="1100" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>
@@ -1882,17 +1928,6 @@
             </a:tabLst>
           </a:pPr>
           <a:r>
-            <a:rPr lang="de-DE" sz="1100" b="1" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>___________________________________________________________________________</a:t>
-          </a:r>
-          <a:r>
             <a:rPr lang="de-DE" sz="1100" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
@@ -1927,7 +1962,7 @@
               <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
-            <a:t> </a:t>
+            <a:t>Der Auftrag wurde ordnungsgemäß nach Kostenvoranschlag  </a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1100" b="0" u="none" strike="noStrike">
             <a:effectLst/>
@@ -1979,7 +2014,7 @@
               <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
-            <a:t>Der Auftrag wurde ordnungsgemäß nach Kostenvoranschlag  </a:t>
+            <a:t>durchgeführt am:  ______________________ </a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1100" b="0" u="none" strike="noStrike">
             <a:effectLst/>
@@ -2031,7 +2066,7 @@
               <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
-            <a:t>durchgeführt am:  ______________________ </a:t>
+            <a:t> </a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1100" b="0" u="none" strike="noStrike">
             <a:effectLst/>
@@ -2161,7 +2196,7 @@
               <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
-            <a:t> </a:t>
+            <a:t>_______________________                                   _____________________________________ </a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1100" b="0" u="none" strike="noStrike">
             <a:effectLst/>
@@ -2179,58 +2214,6 @@
             </a:tabLst>
           </a:pPr>
           <a:r>
-            <a:rPr lang="de-DE" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" u="none" strike="noStrike">
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Times New Roman"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr defTabSz="914400">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:tabLst>
-              <a:tab algn="l" pos="0"/>
-            </a:tabLst>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="de-DE" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>______________________                                                             ______________________ </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" u="none" strike="noStrike">
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Times New Roman"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr defTabSz="914400">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:tabLst>
-              <a:tab algn="l" pos="0"/>
-            </a:tabLst>
-          </a:pPr>
-          <a:r>
             <a:rPr lang="de-DE" sz="900" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
@@ -2239,7 +2222,7 @@
               <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
-            <a:t>Datum, Unterschrift Kunde                                                                                     Datum, Unterschrift Umzugsunternehmen</a:t>
+            <a:t>Datum, Unterschrift Kunde                                          Datum, Unterschrift Umzugsunternehmen</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="900" b="0" u="none" strike="noStrike">
             <a:effectLst/>
@@ -2275,9 +2258,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>545760</xdr:colOff>
+      <xdr:colOff>545400</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>38880</xdr:rowOff>
+      <xdr:rowOff>38520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2290,8 +2273,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5201280" y="371520"/>
-          <a:ext cx="2419560" cy="1575000"/>
+          <a:off x="5200560" y="371520"/>
+          <a:ext cx="2419200" cy="1574640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2480,896 +2463,896 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:N56"/>
   <sheetFormatPr defaultColWidth="11.4296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="5.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="27.72"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="0" width="53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="7.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="20.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="5.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="27.72"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="1" width="53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="7.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="20.43"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="2"/>
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="4"/>
-      <c r="J3" s="0" t="str">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="5"/>
+      <c r="J3" s="1" t="str">
         <f aca="false">A16</f>
         <v>Unverbindlicher Kostenvoranschlag 2026-132</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I4" s="0" t="str">
+      <c r="I4" s="1" t="str">
         <f aca="false">A8</f>
         <v>Herrn</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="I5" s="0" t="str">
+      <c r="B5" s="6"/>
+      <c r="I5" s="1" t="str">
         <f aca="false">A9</f>
         <v>Horst Lindenthal</v>
       </c>
-      <c r="K5" s="0" t="str">
+      <c r="K5" s="1" t="str">
         <f aca="false">F18</f>
         <v>delphinchris007@web.de</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="I6" s="0" t="str">
+      <c r="B6" s="6"/>
+      <c r="I6" s="1" t="str">
         <f aca="false">A17</f>
         <v>Auftragsdatum: </v>
       </c>
-      <c r="J6" s="6" t="str">
+      <c r="J6" s="7" t="str">
         <f aca="false">B17</f>
         <v>KW 13-14</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I7" s="7" t="str">
+      <c r="I7" s="8" t="str">
         <f aca="false">A18</f>
         <v>Kundentelefonnr.: </v>
       </c>
-      <c r="J7" s="8" t="str">
+      <c r="J7" s="9" t="str">
         <f aca="false">B18</f>
         <v>01746555333</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I9" s="0" t="str">
+      <c r="I9" s="1" t="str">
         <f aca="false">A25</f>
         <v>Beladestelle:</v>
       </c>
-      <c r="L9" s="0" t="str">
+      <c r="L9" s="1" t="str">
         <f aca="false">F25</f>
         <v>Entladestelle:</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="I10" s="0" t="str">
+      <c r="B10" s="8"/>
+      <c r="I10" s="1" t="str">
         <f aca="false">A26</f>
         <v>Schlickumerstr. 15A</v>
       </c>
-      <c r="L10" s="0" t="str">
+      <c r="L10" s="1" t="str">
         <f aca="false">F26</f>
         <v>Weinhagenstr. 9</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="I11" s="0" t="str">
+      <c r="B11" s="8"/>
+      <c r="I11" s="1" t="str">
         <f aca="false">A27</f>
         <v>31157 Sarstedt</v>
       </c>
-      <c r="L11" s="9" t="str">
+      <c r="L11" s="10" t="str">
         <f aca="false">F27</f>
         <v>31135 Hildesheim</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I12" s="0" t="str">
+      <c r="I12" s="1" t="str">
         <f aca="false">A28</f>
         <v>2OG mit Fahrstuhl</v>
       </c>
-      <c r="L12" s="0" t="str">
+      <c r="L12" s="1" t="str">
         <f aca="false">F28</f>
         <v>1 OG </v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G14" s="10" t="n">
+      <c r="G14" s="11" t="n">
         <f aca="true">(TODAY())</f>
-        <v>46077</v>
-      </c>
-      <c r="I14" s="0" t="str">
+        <v>46078</v>
+      </c>
+      <c r="I14" s="1" t="str">
         <f aca="false">A29</f>
         <v>Umzugspauschale 15 m³</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11" t="s">
+      <c r="J15" s="12"/>
+      <c r="K15" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="L15" s="12"/>
-      <c r="M15" s="13" t="s">
+      <c r="L15" s="13"/>
+      <c r="M15" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="I16" s="16" t="str">
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="I16" s="17" t="str">
         <f aca="false">A31</f>
         <v>De/Montage</v>
       </c>
-      <c r="J16" s="16"/>
-      <c r="K16" s="17" t="n">
+      <c r="J16" s="17"/>
+      <c r="K16" s="18" t="n">
         <f aca="false">C31</f>
         <v>0</v>
       </c>
-      <c r="L16" s="18"/>
-      <c r="M16" s="18" t="n">
+      <c r="L16" s="19"/>
+      <c r="M16" s="19" t="n">
         <f aca="false">E31</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="19"/>
-      <c r="I17" s="20" t="str">
+      <c r="C17" s="20"/>
+      <c r="I17" s="21" t="str">
         <f aca="false">A32</f>
         <v>Halteverbotszone</v>
       </c>
-      <c r="J17" s="20"/>
-      <c r="K17" s="21" t="str">
+      <c r="J17" s="21"/>
+      <c r="K17" s="22" t="str">
         <f aca="false">C32</f>
         <v> Entladestelle</v>
       </c>
-      <c r="L17" s="22"/>
-      <c r="M17" s="22" t="n">
+      <c r="L17" s="23"/>
+      <c r="M17" s="23" t="n">
         <f aca="false">E32</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="8"/>
-      <c r="E18" s="24" t="s">
+      <c r="C18" s="9"/>
+      <c r="E18" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="F18" s="25" t="s">
+      <c r="F18" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="G18" s="26"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="16" t="str">
+      <c r="G18" s="27"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="17" t="str">
         <f aca="false">A33</f>
         <v>Umzugsmaterial</v>
       </c>
-      <c r="J18" s="16"/>
-      <c r="K18" s="17" t="str">
+      <c r="J18" s="17"/>
+      <c r="K18" s="18" t="str">
         <f aca="false">C33</f>
         <v>Stretchfolie,Decken,Gurte</v>
       </c>
-      <c r="L18" s="18"/>
-      <c r="M18" s="18" t="n">
+      <c r="L18" s="19"/>
+      <c r="M18" s="19" t="n">
         <f aca="false">E33</f>
         <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="28"/>
-      <c r="C19" s="8"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="I19" s="29" t="str">
+      <c r="B19" s="29"/>
+      <c r="C19" s="9"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="I19" s="30" t="str">
         <f aca="false">A34</f>
         <v>Verkauf Seidenpapier</v>
       </c>
-      <c r="J19" s="30"/>
-      <c r="K19" s="21" t="str">
+      <c r="J19" s="31"/>
+      <c r="K19" s="22" t="str">
         <f aca="false">C34</f>
         <v>500x750 </v>
       </c>
-      <c r="L19" s="22"/>
-      <c r="M19" s="22" t="n">
+      <c r="L19" s="23"/>
+      <c r="M19" s="23" t="n">
         <f aca="false">E34</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="31"/>
-      <c r="C20" s="31"/>
-      <c r="G20" s="32"/>
-      <c r="I20" s="16" t="str">
+      <c r="B20" s="32"/>
+      <c r="C20" s="32"/>
+      <c r="G20" s="33"/>
+      <c r="I20" s="17" t="str">
         <f aca="false">A35</f>
         <v>Verkauf U-Karton</v>
       </c>
-      <c r="J20" s="16"/>
-      <c r="K20" s="17" t="str">
+      <c r="J20" s="17"/>
+      <c r="K20" s="18" t="str">
         <f aca="false">C35</f>
         <v>590x318x328</v>
       </c>
-      <c r="L20" s="18"/>
-      <c r="M20" s="18" t="n">
+      <c r="L20" s="19"/>
+      <c r="M20" s="19" t="n">
         <f aca="false">E35</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I21" s="20" t="str">
+      <c r="I21" s="21" t="str">
         <f aca="false">A37</f>
         <v>Verleih Kleiderboxen</v>
       </c>
-      <c r="J21" s="20"/>
-      <c r="K21" s="21" t="str">
+      <c r="J21" s="21"/>
+      <c r="K21" s="22" t="str">
         <f aca="false">C36</f>
         <v>400x318x328</v>
       </c>
-      <c r="L21" s="22"/>
-      <c r="M21" s="22" t="n">
+      <c r="L21" s="23"/>
+      <c r="M21" s="23" t="n">
         <f aca="false">E37</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I22" s="33" t="str">
+      <c r="I22" s="34" t="str">
         <f aca="false">A38</f>
         <v>Personal</v>
       </c>
-      <c r="J22" s="33"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="18"/>
-      <c r="M22" s="18" t="n">
+      <c r="J22" s="34"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="19" t="n">
         <f aca="false">E38</f>
         <v>3</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I23" s="20" t="str">
+      <c r="I23" s="21" t="str">
         <f aca="false">A39</f>
         <v>3,5t Transporter m. Koffer</v>
       </c>
-      <c r="J23" s="20"/>
-      <c r="K23" s="21" t="n">
+      <c r="J23" s="21"/>
+      <c r="K23" s="22" t="n">
         <f aca="false">C39</f>
         <v>0</v>
       </c>
-      <c r="L23" s="22"/>
-      <c r="M23" s="22" t="n">
+      <c r="L23" s="23"/>
+      <c r="M23" s="23" t="n">
         <f aca="false">E39</f>
         <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I24" s="16" t="str">
+      <c r="I24" s="17" t="str">
         <f aca="false">A41</f>
         <v>Transferfahrzeug</v>
       </c>
-      <c r="J24" s="16"/>
-      <c r="K24" s="17" t="n">
+      <c r="J24" s="17"/>
+      <c r="K24" s="18" t="n">
         <f aca="false">C41</f>
         <v>0</v>
       </c>
-      <c r="L24" s="18"/>
-      <c r="M24" s="18" t="n">
+      <c r="L24" s="19"/>
+      <c r="M24" s="19" t="n">
         <f aca="false">E41</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="34" t="s">
+      <c r="A25" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="B25" s="34"/>
-      <c r="D25" s="35" t="s">
+      <c r="B25" s="35"/>
+      <c r="D25" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="F25" s="36" t="s">
+      <c r="F25" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="G25" s="36"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="37"/>
-      <c r="J25" s="37"/>
-      <c r="K25" s="21"/>
-      <c r="L25" s="22"/>
-      <c r="M25" s="22"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="23"/>
+      <c r="M25" s="23"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="38" t="str">
+      <c r="A26" s="39" t="str">
         <f aca="false">A10</f>
         <v>Schlickumerstr. 15A</v>
       </c>
-      <c r="B26" s="38"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="35"/>
-      <c r="F26" s="39" t="s">
+      <c r="B26" s="39"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="36"/>
+      <c r="F26" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="G26" s="39"/>
+      <c r="G26" s="40"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="38" t="str">
+      <c r="A27" s="39" t="str">
         <f aca="false">A11</f>
         <v>31157 Sarstedt</v>
       </c>
-      <c r="B27" s="38"/>
-      <c r="D27" s="35"/>
-      <c r="F27" s="40" t="s">
+      <c r="B27" s="39"/>
+      <c r="D27" s="36"/>
+      <c r="F27" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="G27" s="41"/>
-      <c r="H27" s="42"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="43"/>
     </row>
     <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="43" t="s">
+      <c r="A28" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="B28" s="44"/>
-      <c r="D28" s="35"/>
-      <c r="F28" s="0" t="s">
+      <c r="B28" s="45"/>
+      <c r="D28" s="36"/>
+      <c r="F28" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G28" s="45"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="46"/>
-      <c r="J28" s="46"/>
-      <c r="K28" s="46"/>
-      <c r="L28" s="46"/>
-      <c r="M28" s="46"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="47"/>
+      <c r="K28" s="47"/>
+      <c r="L28" s="47"/>
+      <c r="M28" s="47"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="47" t="s">
+      <c r="A29" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="47"/>
-      <c r="C29" s="47"/>
-      <c r="D29" s="47"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="47"/>
-      <c r="I29" s="46"/>
-      <c r="J29" s="46"/>
-      <c r="K29" s="46"/>
-      <c r="L29" s="46"/>
-      <c r="M29" s="46"/>
-      <c r="N29" s="48"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="48"/>
+      <c r="D29" s="48"/>
+      <c r="E29" s="48"/>
+      <c r="F29" s="48"/>
+      <c r="G29" s="48"/>
+      <c r="I29" s="47"/>
+      <c r="J29" s="47"/>
+      <c r="K29" s="47"/>
+      <c r="L29" s="47"/>
+      <c r="M29" s="47"/>
+      <c r="N29" s="49"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="49" t="s">
+      <c r="A30" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="49"/>
-      <c r="C30" s="50" t="s">
+      <c r="B30" s="50"/>
+      <c r="C30" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="D30" s="27"/>
-      <c r="E30" s="51" t="s">
+      <c r="D30" s="28"/>
+      <c r="E30" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="F30" s="35" t="s">
+      <c r="F30" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="G30" s="51" t="s">
+      <c r="G30" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="I30" s="46"/>
-      <c r="J30" s="46"/>
-      <c r="K30" s="46"/>
-      <c r="L30" s="46"/>
-      <c r="M30" s="46"/>
-      <c r="N30" s="52"/>
+      <c r="I30" s="47"/>
+      <c r="J30" s="47"/>
+      <c r="K30" s="47"/>
+      <c r="L30" s="47"/>
+      <c r="M30" s="47"/>
+      <c r="N30" s="53"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="53" t="s">
+      <c r="A31" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="53"/>
-      <c r="C31" s="54"/>
-      <c r="D31" s="55"/>
-      <c r="E31" s="55" t="n">
+      <c r="B31" s="54"/>
+      <c r="C31" s="55"/>
+      <c r="D31" s="56"/>
+      <c r="E31" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="F31" s="56" t="n">
+      <c r="F31" s="57" t="n">
         <v>50</v>
       </c>
-      <c r="G31" s="56" t="n">
+      <c r="G31" s="57" t="n">
         <f aca="false">IF(E31="", 0, F31*E31)</f>
         <v>0</v>
       </c>
-      <c r="N31" s="57"/>
+      <c r="N31" s="58"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="58" t="s">
+      <c r="A32" s="59" t="s">
         <v>30</v>
       </c>
-      <c r="B32" s="58"/>
-      <c r="C32" s="59" t="s">
+      <c r="B32" s="59"/>
+      <c r="C32" s="60" t="s">
         <v>31</v>
       </c>
-      <c r="D32" s="60"/>
-      <c r="E32" s="60" t="n">
+      <c r="D32" s="61"/>
+      <c r="E32" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="F32" s="61" t="n">
+      <c r="F32" s="62" t="n">
         <v>100</v>
       </c>
-      <c r="G32" s="61" t="n">
+      <c r="G32" s="62" t="n">
         <f aca="false">IF(E32="", 0, F32*E32)</f>
         <v>0</v>
       </c>
-      <c r="I32" s="62"/>
-      <c r="J32" s="62"/>
-      <c r="K32" s="62"/>
-      <c r="L32" s="62"/>
-      <c r="M32" s="62"/>
+      <c r="I32" s="63"/>
+      <c r="J32" s="63"/>
+      <c r="K32" s="63"/>
+      <c r="L32" s="63"/>
+      <c r="M32" s="63"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="53" t="s">
+      <c r="A33" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="53"/>
-      <c r="C33" s="54" t="s">
+      <c r="B33" s="54"/>
+      <c r="C33" s="55" t="s">
         <v>33</v>
       </c>
-      <c r="D33" s="55"/>
-      <c r="E33" s="55" t="n">
+      <c r="D33" s="56"/>
+      <c r="E33" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="F33" s="56" t="n">
+      <c r="F33" s="57" t="n">
         <v>30</v>
       </c>
-      <c r="G33" s="56" t="n">
+      <c r="G33" s="57" t="n">
         <f aca="false">IF(E33="", 0, F33*E33)</f>
         <v>30</v>
       </c>
-      <c r="I33" s="62"/>
-      <c r="J33" s="62"/>
-      <c r="K33" s="62"/>
-      <c r="L33" s="62"/>
-      <c r="M33" s="62"/>
+      <c r="I33" s="63"/>
+      <c r="J33" s="63"/>
+      <c r="K33" s="63"/>
+      <c r="L33" s="63"/>
+      <c r="M33" s="63"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="63" t="s">
+      <c r="A34" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="63"/>
-      <c r="C34" s="59" t="s">
+      <c r="B34" s="64"/>
+      <c r="C34" s="60" t="s">
         <v>35</v>
       </c>
-      <c r="D34" s="60"/>
-      <c r="E34" s="60" t="n">
+      <c r="D34" s="61"/>
+      <c r="E34" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="F34" s="61" t="n">
+      <c r="F34" s="62" t="n">
         <v>5</v>
       </c>
-      <c r="G34" s="61" t="n">
+      <c r="G34" s="62" t="n">
         <f aca="false">IF(E34="", 0, F34*E34)</f>
         <v>0</v>
       </c>
-      <c r="I34" s="62"/>
-      <c r="J34" s="62"/>
-      <c r="K34" s="62"/>
-      <c r="L34" s="62"/>
-      <c r="M34" s="62"/>
+      <c r="I34" s="63"/>
+      <c r="J34" s="63"/>
+      <c r="K34" s="63"/>
+      <c r="L34" s="63"/>
+      <c r="M34" s="63"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="53" t="s">
+      <c r="A35" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="53"/>
-      <c r="C35" s="54" t="s">
+      <c r="B35" s="54"/>
+      <c r="C35" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="D35" s="55"/>
-      <c r="E35" s="55" t="n">
+      <c r="D35" s="56"/>
+      <c r="E35" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="F35" s="56" t="n">
+      <c r="F35" s="57" t="n">
         <v>2.1</v>
       </c>
-      <c r="G35" s="56" t="n">
+      <c r="G35" s="57" t="n">
         <f aca="false">IF(E35="", 0, F35*E35)</f>
         <v>0</v>
       </c>
-      <c r="I35" s="62"/>
-      <c r="J35" s="62"/>
-      <c r="K35" s="62"/>
-      <c r="L35" s="62"/>
-      <c r="M35" s="62"/>
+      <c r="I35" s="63"/>
+      <c r="J35" s="63"/>
+      <c r="K35" s="63"/>
+      <c r="L35" s="63"/>
+      <c r="M35" s="63"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="64" t="s">
+      <c r="A36" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="64"/>
-      <c r="C36" s="59" t="s">
+      <c r="B36" s="65"/>
+      <c r="C36" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="D36" s="60"/>
-      <c r="E36" s="60" t="n">
+      <c r="D36" s="61"/>
+      <c r="E36" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="F36" s="61" t="n">
+      <c r="F36" s="62" t="n">
         <v>2.2</v>
       </c>
-      <c r="G36" s="61" t="n">
+      <c r="G36" s="62" t="n">
         <f aca="false">IF(E36="", 0, F36*E36)</f>
         <v>0</v>
       </c>
-      <c r="I36" s="62"/>
-      <c r="J36" s="62"/>
-      <c r="K36" s="62"/>
-      <c r="L36" s="62"/>
-      <c r="M36" s="62"/>
+      <c r="I36" s="63"/>
+      <c r="J36" s="63"/>
+      <c r="K36" s="63"/>
+      <c r="L36" s="63"/>
+      <c r="M36" s="63"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="53" t="s">
+      <c r="A37" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="53"/>
-      <c r="C37" s="65" t="s">
+      <c r="B37" s="54"/>
+      <c r="C37" s="66" t="s">
         <v>41</v>
       </c>
-      <c r="D37" s="55"/>
-      <c r="E37" s="55" t="n">
+      <c r="D37" s="56"/>
+      <c r="E37" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="F37" s="56" t="n">
+      <c r="F37" s="57" t="n">
         <v>10</v>
       </c>
-      <c r="G37" s="56" t="n">
+      <c r="G37" s="57" t="n">
         <f aca="false">IF(E37="", 0, F37*E37)</f>
         <v>0</v>
       </c>
-      <c r="I37" s="62"/>
-      <c r="J37" s="62"/>
-      <c r="K37" s="62"/>
-      <c r="L37" s="62"/>
-      <c r="M37" s="62"/>
+      <c r="I37" s="63"/>
+      <c r="J37" s="63"/>
+      <c r="K37" s="63"/>
+      <c r="L37" s="63"/>
+      <c r="M37" s="63"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="66" t="s">
+      <c r="A38" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="66"/>
-      <c r="C38" s="59"/>
-      <c r="D38" s="60" t="s">
+      <c r="B38" s="67"/>
+      <c r="C38" s="60"/>
+      <c r="D38" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="E38" s="60" t="n">
+      <c r="E38" s="61" t="n">
         <v>3</v>
       </c>
-      <c r="F38" s="61" t="n">
+      <c r="F38" s="62" t="n">
         <v>28</v>
       </c>
-      <c r="G38" s="61" t="n">
+      <c r="G38" s="62" t="n">
         <f aca="false">IF(E38="", 0, F38*E38*J50)</f>
         <v>0</v>
       </c>
-      <c r="I38" s="62"/>
-      <c r="J38" s="62"/>
-      <c r="K38" s="62"/>
-      <c r="L38" s="62"/>
-      <c r="M38" s="62"/>
+      <c r="I38" s="63"/>
+      <c r="J38" s="63"/>
+      <c r="K38" s="63"/>
+      <c r="L38" s="63"/>
+      <c r="M38" s="63"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="53" t="s">
+      <c r="A39" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="B39" s="53"/>
-      <c r="C39" s="54"/>
-      <c r="D39" s="55"/>
-      <c r="E39" s="55" t="n">
+      <c r="B39" s="54"/>
+      <c r="C39" s="55"/>
+      <c r="D39" s="56"/>
+      <c r="E39" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="56" t="n">
+      <c r="F39" s="57" t="n">
         <v>60</v>
       </c>
-      <c r="G39" s="56" t="n">
+      <c r="G39" s="57" t="n">
         <f aca="false">IF(E39="", 0, F39*E39)</f>
         <v>60</v>
       </c>
-      <c r="I39" s="62"/>
-      <c r="J39" s="62"/>
-      <c r="K39" s="62"/>
-      <c r="L39" s="62"/>
-      <c r="M39" s="62"/>
-      <c r="N39" s="52"/>
+      <c r="I39" s="63"/>
+      <c r="J39" s="63"/>
+      <c r="K39" s="63"/>
+      <c r="L39" s="63"/>
+      <c r="M39" s="63"/>
+      <c r="N39" s="53"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="64" t="s">
+      <c r="A40" s="65" t="s">
         <v>45</v>
       </c>
-      <c r="B40" s="64"/>
-      <c r="C40" s="59"/>
-      <c r="D40" s="60"/>
-      <c r="E40" s="60" t="n">
+      <c r="B40" s="65"/>
+      <c r="C40" s="60"/>
+      <c r="D40" s="61"/>
+      <c r="E40" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="F40" s="61" t="n">
+      <c r="F40" s="62" t="n">
         <v>300</v>
       </c>
-      <c r="G40" s="61" t="n">
+      <c r="G40" s="62" t="n">
         <f aca="false">IF(E40="", 0, F40*E40)</f>
         <v>0</v>
       </c>
-      <c r="I40" s="62"/>
-      <c r="J40" s="62"/>
-      <c r="K40" s="62"/>
-      <c r="L40" s="62"/>
-      <c r="M40" s="62"/>
-      <c r="N40" s="52"/>
+      <c r="I40" s="63"/>
+      <c r="J40" s="63"/>
+      <c r="K40" s="63"/>
+      <c r="L40" s="63"/>
+      <c r="M40" s="63"/>
+      <c r="N40" s="53"/>
     </row>
     <row r="41" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="53" t="s">
+      <c r="A41" s="54" t="s">
         <v>46</v>
       </c>
-      <c r="B41" s="53"/>
-      <c r="C41" s="54"/>
-      <c r="D41" s="55" t="s">
+      <c r="B41" s="54"/>
+      <c r="C41" s="55"/>
+      <c r="D41" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="E41" s="55" t="n">
+      <c r="E41" s="56" t="n">
         <v>0</v>
       </c>
-      <c r="F41" s="56" t="n">
+      <c r="F41" s="57" t="n">
         <v>45</v>
       </c>
-      <c r="G41" s="56" t="n">
+      <c r="G41" s="57" t="n">
         <f aca="false">IF(E41="", 0, F41*E41)</f>
         <v>0</v>
       </c>
-      <c r="I41" s="62"/>
-      <c r="J41" s="62"/>
-      <c r="K41" s="62"/>
-      <c r="L41" s="62"/>
-      <c r="M41" s="62"/>
-      <c r="N41" s="60"/>
+      <c r="I41" s="63"/>
+      <c r="J41" s="63"/>
+      <c r="K41" s="63"/>
+      <c r="L41" s="63"/>
+      <c r="M41" s="63"/>
+      <c r="N41" s="61"/>
     </row>
     <row r="42" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="58" t="s">
+      <c r="A42" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="B42" s="58"/>
-      <c r="C42" s="59"/>
-      <c r="D42" s="60" t="s">
+      <c r="B42" s="59"/>
+      <c r="C42" s="60"/>
+      <c r="D42" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="E42" s="60" t="n">
+      <c r="E42" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="F42" s="61" t="n">
+      <c r="F42" s="62" t="n">
         <v>30</v>
       </c>
-      <c r="G42" s="61" t="n">
+      <c r="G42" s="62" t="n">
         <f aca="false">IF(E42="", 0, F42*E42)</f>
         <v>30</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="7"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="67"/>
-      <c r="D43" s="68"/>
-      <c r="E43" s="68"/>
-      <c r="F43" s="68"/>
-      <c r="G43" s="68"/>
+      <c r="A43" s="8"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="68"/>
+      <c r="D43" s="69"/>
+      <c r="E43" s="69"/>
+      <c r="F43" s="69"/>
+      <c r="G43" s="69"/>
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="7"/>
-      <c r="C44" s="69" t="s">
+      <c r="A44" s="8"/>
+      <c r="C44" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="D44" s="68"/>
-      <c r="E44" s="70"/>
-      <c r="F44" s="70"/>
-      <c r="G44" s="71" t="n">
+      <c r="D44" s="69"/>
+      <c r="E44" s="71"/>
+      <c r="F44" s="71"/>
+      <c r="G44" s="72" t="n">
         <f aca="false">G31+G32+G33+G34+G35+G37+G38+G39+G41+G42+G40</f>
         <v>120</v>
       </c>
-      <c r="J44" s="52"/>
-    </row>
-    <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7"/>
-      <c r="C45" s="69" t="s">
+      <c r="J44" s="53"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="8"/>
+      <c r="C45" s="70" t="s">
         <v>50</v>
       </c>
-      <c r="D45" s="68"/>
-      <c r="E45" s="70"/>
-      <c r="F45" s="70"/>
-      <c r="G45" s="71" t="n">
+      <c r="D45" s="69"/>
+      <c r="E45" s="71"/>
+      <c r="F45" s="71"/>
+      <c r="G45" s="72" t="n">
         <f aca="false">G44*19%</f>
         <v>22.8</v>
       </c>
-      <c r="J45" s="52"/>
-      <c r="M45" s="72"/>
+      <c r="J45" s="53"/>
+      <c r="M45" s="73"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C46" s="0" t="s">
+      <c r="C46" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E46" s="73"/>
-      <c r="F46" s="73"/>
-      <c r="G46" s="74" t="n">
+      <c r="E46" s="74"/>
+      <c r="F46" s="74"/>
+      <c r="G46" s="75" t="n">
         <f aca="false">G44+G45</f>
         <v>142.8</v>
       </c>
-      <c r="J46" s="52"/>
-      <c r="M46" s="72"/>
+      <c r="J46" s="53"/>
+      <c r="M46" s="73"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J47" s="52"/>
-      <c r="M47" s="72"/>
+      <c r="J47" s="53"/>
+      <c r="M47" s="73"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="46"/>
-      <c r="B48" s="46"/>
-      <c r="C48" s="46"/>
-      <c r="D48" s="46"/>
-      <c r="E48" s="46"/>
-      <c r="F48" s="46"/>
-      <c r="G48" s="46"/>
-      <c r="J48" s="52"/>
-      <c r="M48" s="72"/>
+      <c r="A48" s="47"/>
+      <c r="B48" s="47"/>
+      <c r="C48" s="47"/>
+      <c r="D48" s="47"/>
+      <c r="E48" s="47"/>
+      <c r="F48" s="47"/>
+      <c r="G48" s="47"/>
+      <c r="J48" s="53"/>
+      <c r="M48" s="73"/>
     </row>
     <row r="49" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="46"/>
-      <c r="B49" s="46"/>
-      <c r="C49" s="46"/>
-      <c r="D49" s="46"/>
-      <c r="E49" s="46"/>
-      <c r="F49" s="46"/>
-      <c r="G49" s="46"/>
-      <c r="J49" s="52"/>
-      <c r="M49" s="72"/>
+      <c r="A49" s="47"/>
+      <c r="B49" s="47"/>
+      <c r="C49" s="47"/>
+      <c r="D49" s="47"/>
+      <c r="E49" s="47"/>
+      <c r="F49" s="47"/>
+      <c r="G49" s="47"/>
+      <c r="J49" s="53"/>
+      <c r="M49" s="73"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="46"/>
-      <c r="B50" s="46"/>
-      <c r="C50" s="46"/>
-      <c r="D50" s="46"/>
-      <c r="E50" s="46"/>
-      <c r="F50" s="46"/>
-      <c r="G50" s="46"/>
-      <c r="J50" s="75"/>
-      <c r="M50" s="76"/>
+      <c r="A50" s="47"/>
+      <c r="B50" s="47"/>
+      <c r="C50" s="47"/>
+      <c r="D50" s="47"/>
+      <c r="E50" s="47"/>
+      <c r="F50" s="47"/>
+      <c r="G50" s="47"/>
+      <c r="J50" s="76"/>
+      <c r="M50" s="77"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="46"/>
-      <c r="B51" s="46"/>
-      <c r="C51" s="46"/>
-      <c r="D51" s="46"/>
-      <c r="E51" s="46"/>
-      <c r="F51" s="46"/>
-      <c r="G51" s="46"/>
-      <c r="J51" s="52"/>
-      <c r="M51" s="76"/>
+      <c r="A51" s="47"/>
+      <c r="B51" s="47"/>
+      <c r="C51" s="47"/>
+      <c r="D51" s="47"/>
+      <c r="E51" s="47"/>
+      <c r="F51" s="47"/>
+      <c r="G51" s="47"/>
+      <c r="J51" s="53"/>
+      <c r="M51" s="77"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="46"/>
-      <c r="B52" s="46"/>
-      <c r="C52" s="46"/>
-      <c r="D52" s="46"/>
-      <c r="E52" s="46"/>
-      <c r="F52" s="46"/>
-      <c r="G52" s="46"/>
+      <c r="A52" s="47"/>
+      <c r="B52" s="47"/>
+      <c r="C52" s="47"/>
+      <c r="D52" s="47"/>
+      <c r="E52" s="47"/>
+      <c r="F52" s="47"/>
+      <c r="G52" s="47"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="46"/>
-      <c r="B53" s="46"/>
-      <c r="C53" s="46"/>
-      <c r="D53" s="46"/>
-      <c r="E53" s="46"/>
-      <c r="F53" s="46"/>
-      <c r="G53" s="46"/>
+      <c r="A53" s="47"/>
+      <c r="B53" s="47"/>
+      <c r="C53" s="47"/>
+      <c r="D53" s="47"/>
+      <c r="E53" s="47"/>
+      <c r="F53" s="47"/>
+      <c r="G53" s="47"/>
     </row>
     <row r="54" customFormat="false" ht="2.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="46"/>
-      <c r="B54" s="46"/>
-      <c r="C54" s="46"/>
-      <c r="D54" s="46"/>
-      <c r="E54" s="46"/>
-      <c r="F54" s="46"/>
-      <c r="G54" s="46"/>
+      <c r="A54" s="47"/>
+      <c r="B54" s="47"/>
+      <c r="C54" s="47"/>
+      <c r="D54" s="47"/>
+      <c r="E54" s="47"/>
+      <c r="F54" s="47"/>
+      <c r="G54" s="47"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="46"/>
-      <c r="B55" s="46"/>
-      <c r="C55" s="46"/>
-      <c r="D55" s="46"/>
-      <c r="E55" s="46"/>
-      <c r="F55" s="46"/>
-      <c r="G55" s="46"/>
-      <c r="J55" s="77"/>
+      <c r="A55" s="47"/>
+      <c r="B55" s="47"/>
+      <c r="C55" s="47"/>
+      <c r="D55" s="47"/>
+      <c r="E55" s="47"/>
+      <c r="F55" s="47"/>
+      <c r="G55" s="47"/>
+      <c r="J55" s="78"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="46"/>
-      <c r="B56" s="46"/>
-      <c r="C56" s="46"/>
-      <c r="D56" s="46"/>
-      <c r="E56" s="46"/>
-      <c r="F56" s="46"/>
-      <c r="G56" s="46"/>
+      <c r="A56" s="47"/>
+      <c r="B56" s="47"/>
+      <c r="C56" s="47"/>
+      <c r="D56" s="47"/>
+      <c r="E56" s="47"/>
+      <c r="F56" s="47"/>
+      <c r="G56" s="47"/>
     </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="38">
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B6"/>
@@ -3405,6 +3388,9 @@
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="A48:G49"/>
     <mergeCell ref="A50:G56"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A40:B40"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E18" r:id="rId1" display="E-Mail: "/>

--- a/templates/offer_template.xlsx
+++ b/templates/offer_template.xlsx
@@ -216,7 +216,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="[$-409]mmmm\ d&quot;, &quot;yyyy;@"/>
     <numFmt numFmtId="166" formatCode="[&lt;=9999999]###\-####;\(###&quot;) &quot;###\-####"/>
@@ -225,6 +225,7 @@
     <numFmt numFmtId="169" formatCode="_-* #,##0.00\ [$€-407]_-;\-* #,##0.00\ [$€-407]_-;_-* \-??\ [$€-407]_-;_-@_-"/>
     <numFmt numFmtId="170" formatCode="#,##0&quot; €&quot;;[RED]\-#,##0&quot; €&quot;"/>
     <numFmt numFmtId="171" formatCode="_-* #,##0.00&quot; €&quot;_-;\-* #,##0.00&quot; €&quot;_-;_-* \-??&quot; €&quot;_-;_-@_-"/>
+    <numFmt numFmtId="172" formatCode="#,##0.00&quot; €/Stunde&quot;"/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -541,7 +542,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="87">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -687,7 +688,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -766,7 +767,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true" applyNumberFormat="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -786,7 +787,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true" applyNumberFormat="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -831,7 +832,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="17" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="17" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -843,7 +844,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="17" fillId="0" borderId="0" xfId="17" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -868,6 +869,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>

--- a/templates/offer_template.xlsx
+++ b/templates/offer_template.xlsx
@@ -1294,29 +1294,6 @@
               <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
-            <a:t>- Kartons werden Vorzeitig Geliefert und Werden nach dem Umzug mit 2€ Je Woche berechnet</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" u="none" strike="noStrike">
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Times New Roman"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr>
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="de-DE" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
             <a:t>- Massive Holzmöbel / Designermöbel müssen gesondert benannt werden </a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1100" b="0" u="none" strike="noStrike">

--- a/templates/offer_template.xlsx
+++ b/templates/offer_template.xlsx
@@ -3093,7 +3093,7 @@
         <v>28</v>
       </c>
       <c r="G38" s="62" t="n">
-        <f aca="false">IF(E38="", 0, F38*E38*J50)</f>
+        <f aca="false">IF(E38="", 0, F38*E38*J58)</f>
         <v>0</v>
       </c>
       <c r="I38" s="63"/>
@@ -3196,143 +3196,190 @@
         <v>30</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="8"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="68"/>
-      <c r="D43" s="69"/>
-      <c r="E43" s="69"/>
-      <c r="F43" s="69"/>
-      <c r="G43" s="69"/>
-    </row>
-    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="8"/>
-      <c r="C44" s="70" t="s">
+    <row r="43" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="54"/>
+      <c r="B43" s="54"/>
+      <c r="C43" s="55"/>
+      <c r="D43" s="56"/>
+      <c r="E43" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="57" t="n">
+        <f aca="false">IF(E43="", 0, F43*E43)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="59"/>
+      <c r="B44" s="59"/>
+      <c r="C44" s="60"/>
+      <c r="D44" s="61"/>
+      <c r="E44" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="62" t="n">
+        <f aca="false">IF(E44="", 0, F44*E44)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="54"/>
+      <c r="B45" s="54"/>
+      <c r="C45" s="55"/>
+      <c r="D45" s="56"/>
+      <c r="E45" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="57" t="n">
+        <f aca="false">IF(E45="", 0, F45*E45)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="59"/>
+      <c r="B46" s="59"/>
+      <c r="C46" s="60"/>
+      <c r="D46" s="61"/>
+      <c r="E46" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="62" t="n">
+        <f aca="false">IF(E46="", 0, F46*E46)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="54"/>
+      <c r="B47" s="54"/>
+      <c r="C47" s="55"/>
+      <c r="D47" s="56"/>
+      <c r="E47" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="57" t="n">
+        <f aca="false">IF(E47="", 0, F47*E47)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="59"/>
+      <c r="B48" s="59"/>
+      <c r="C48" s="60"/>
+      <c r="D48" s="61"/>
+      <c r="E48" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="62" t="n">
+        <f aca="false">IF(E48="", 0, F48*E48)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="54"/>
+      <c r="B49" s="54"/>
+      <c r="C49" s="55"/>
+      <c r="D49" s="56"/>
+      <c r="E49" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="57" t="n">
+        <f aca="false">IF(E49="", 0, F49*E49)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="59"/>
+      <c r="B50" s="59"/>
+      <c r="C50" s="60"/>
+      <c r="D50" s="61"/>
+      <c r="E50" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="62" t="n">
+        <f aca="false">IF(E50="", 0, F50*E50)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="8"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="68"/>
+      <c r="D51" s="69"/>
+      <c r="E51" s="69"/>
+      <c r="F51" s="69"/>
+      <c r="G51" s="69"/>
+    </row>
+    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="8"/>
+      <c r="C52" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="D44" s="69"/>
-      <c r="E44" s="71"/>
-      <c r="F44" s="71"/>
-      <c r="G44" s="72" t="n">
+      <c r="D52" s="69"/>
+      <c r="E52" s="71"/>
+      <c r="F52" s="71"/>
+      <c r="G52" s="72" t="n">
         <f aca="false">G31+G32+G33+G34+G35+G37+G38+G39+G41+G42+G40</f>
         <v>120</v>
       </c>
-      <c r="J44" s="53"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="8"/>
-      <c r="C45" s="70" t="s">
+      <c r="J52" s="53"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="8"/>
+      <c r="C53" s="70" t="s">
         <v>50</v>
       </c>
-      <c r="D45" s="69"/>
-      <c r="E45" s="71"/>
-      <c r="F45" s="71"/>
-      <c r="G45" s="72" t="n">
-        <f aca="false">G44*19%</f>
+      <c r="D53" s="69"/>
+      <c r="E53" s="71"/>
+      <c r="F53" s="71"/>
+      <c r="G53" s="72" t="n">
+        <f aca="false">G52*19%</f>
         <v>22.8</v>
       </c>
-      <c r="J45" s="53"/>
-      <c r="M45" s="73"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C46" s="1" t="s">
+      <c r="J53" s="53"/>
+      <c r="M53" s="73"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C54" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E46" s="74"/>
-      <c r="F46" s="74"/>
-      <c r="G46" s="75" t="n">
-        <f aca="false">G44+G45</f>
+      <c r="E54" s="74"/>
+      <c r="F54" s="74"/>
+      <c r="G54" s="75" t="n">
+        <f aca="false">G52+G53</f>
         <v>142.8</v>
       </c>
-      <c r="J46" s="53"/>
-      <c r="M46" s="73"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J47" s="53"/>
-      <c r="M47" s="73"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="47"/>
-      <c r="B48" s="47"/>
-      <c r="C48" s="47"/>
-      <c r="D48" s="47"/>
-      <c r="E48" s="47"/>
-      <c r="F48" s="47"/>
-      <c r="G48" s="47"/>
-      <c r="J48" s="53"/>
-      <c r="M48" s="73"/>
-    </row>
-    <row r="49" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="47"/>
-      <c r="B49" s="47"/>
-      <c r="C49" s="47"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="47"/>
-      <c r="F49" s="47"/>
-      <c r="G49" s="47"/>
-      <c r="J49" s="53"/>
-      <c r="M49" s="73"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="47"/>
-      <c r="B50" s="47"/>
-      <c r="C50" s="47"/>
-      <c r="D50" s="47"/>
-      <c r="E50" s="47"/>
-      <c r="F50" s="47"/>
-      <c r="G50" s="47"/>
-      <c r="J50" s="76"/>
-      <c r="M50" s="77"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="47"/>
-      <c r="B51" s="47"/>
-      <c r="C51" s="47"/>
-      <c r="D51" s="47"/>
-      <c r="E51" s="47"/>
-      <c r="F51" s="47"/>
-      <c r="G51" s="47"/>
-      <c r="J51" s="53"/>
-      <c r="M51" s="77"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="47"/>
-      <c r="B52" s="47"/>
-      <c r="C52" s="47"/>
-      <c r="D52" s="47"/>
-      <c r="E52" s="47"/>
-      <c r="F52" s="47"/>
-      <c r="G52" s="47"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="47"/>
-      <c r="B53" s="47"/>
-      <c r="C53" s="47"/>
-      <c r="D53" s="47"/>
-      <c r="E53" s="47"/>
-      <c r="F53" s="47"/>
-      <c r="G53" s="47"/>
-    </row>
-    <row r="54" customFormat="false" ht="2.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="47"/>
-      <c r="B54" s="47"/>
-      <c r="C54" s="47"/>
-      <c r="D54" s="47"/>
-      <c r="E54" s="47"/>
-      <c r="F54" s="47"/>
-      <c r="G54" s="47"/>
+      <c r="J54" s="53"/>
+      <c r="M54" s="73"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="47"/>
-      <c r="B55" s="47"/>
-      <c r="C55" s="47"/>
-      <c r="D55" s="47"/>
-      <c r="E55" s="47"/>
-      <c r="F55" s="47"/>
-      <c r="G55" s="47"/>
-      <c r="J55" s="78"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J55" s="53"/>
+      <c r="M55" s="73"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="47"/>
       <c r="B56" s="47"/>
       <c r="C56" s="47"/>
@@ -3340,9 +3387,90 @@
       <c r="E56" s="47"/>
       <c r="F56" s="47"/>
       <c r="G56" s="47"/>
+      <c r="J56" s="53"/>
+      <c r="M56" s="73"/>
+    </row>
+    <row r="57" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="47"/>
+      <c r="B57" s="47"/>
+      <c r="C57" s="47"/>
+      <c r="D57" s="47"/>
+      <c r="E57" s="47"/>
+      <c r="F57" s="47"/>
+      <c r="G57" s="47"/>
+      <c r="J57" s="53"/>
+      <c r="M57" s="73"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="47"/>
+      <c r="B58" s="47"/>
+      <c r="C58" s="47"/>
+      <c r="D58" s="47"/>
+      <c r="E58" s="47"/>
+      <c r="F58" s="47"/>
+      <c r="G58" s="47"/>
+      <c r="J58" s="76"/>
+      <c r="M58" s="77"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="47"/>
+      <c r="B59" s="47"/>
+      <c r="C59" s="47"/>
+      <c r="D59" s="47"/>
+      <c r="E59" s="47"/>
+      <c r="F59" s="47"/>
+      <c r="G59" s="47"/>
+      <c r="J59" s="53"/>
+      <c r="M59" s="77"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="47"/>
+      <c r="B60" s="47"/>
+      <c r="C60" s="47"/>
+      <c r="D60" s="47"/>
+      <c r="E60" s="47"/>
+      <c r="F60" s="47"/>
+      <c r="G60" s="47"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="47"/>
+      <c r="B61" s="47"/>
+      <c r="C61" s="47"/>
+      <c r="D61" s="47"/>
+      <c r="E61" s="47"/>
+      <c r="F61" s="47"/>
+      <c r="G61" s="47"/>
+    </row>
+    <row r="62" customFormat="false" ht="2.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="47"/>
+      <c r="B62" s="47"/>
+      <c r="C62" s="47"/>
+      <c r="D62" s="47"/>
+      <c r="E62" s="47"/>
+      <c r="F62" s="47"/>
+      <c r="G62" s="47"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="47"/>
+      <c r="B63" s="47"/>
+      <c r="C63" s="47"/>
+      <c r="D63" s="47"/>
+      <c r="E63" s="47"/>
+      <c r="F63" s="47"/>
+      <c r="G63" s="47"/>
+      <c r="J63" s="78"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="47"/>
+      <c r="B64" s="47"/>
+      <c r="C64" s="47"/>
+      <c r="D64" s="47"/>
+      <c r="E64" s="47"/>
+      <c r="F64" s="47"/>
+      <c r="G64" s="47"/>
     </row>
   </sheetData>
-  <mergeCells count="38">
+  <mergeCells count="46">
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B6"/>
@@ -3368,7 +3496,7 @@
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="A32:B32"/>
-    <mergeCell ref="I32:M41"/>
+    <mergeCell ref="I32:M49"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="A37:B37"/>
@@ -3376,11 +3504,19 @@
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A48:G49"/>
-    <mergeCell ref="A50:G56"/>
+    <mergeCell ref="A56:G57"/>
+    <mergeCell ref="A58:G64"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E18" r:id="rId1" display="E-Mail: "/>

--- a/templates/offer_template.xlsx
+++ b/templates/offer_template.xlsx
@@ -542,7 +542,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="88">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -882,6 +882,10 @@
     </xf>
     <xf numFmtId="172" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -966,13 +970,13 @@
   <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>797040</xdr:colOff>
+      <xdr:colOff>925056</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>79560</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>704160</xdr:colOff>
+      <xdr:colOff>832176</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>185040</xdr:rowOff>
     </xdr:to>
@@ -2239,19 +2243,14 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>434880</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>95400</xdr:rowOff>
+      <xdr:colOff>638266</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>169284</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>545400</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>38520</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="2500000" cy="1653578"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Grafik 2"/>
@@ -2264,7 +2263,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5200560" y="371520"/>
-          <a:ext cx="2419200" cy="1574640"/>
+          <a:ext cx="2500000" cy="1653578"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2276,7 +2275,7 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2473,7 +2472,11 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Aust Umzüge und Haushaltsauflösungen</t>
+        </is>
+      </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -2481,7 +2484,11 @@
       <c r="F2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4"/>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Ihr Umzug in besten Händen bei Aust!</t>
+        </is>
+      </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>

--- a/templates/offer_template.xlsx
+++ b/templates/offer_template.xlsx
@@ -542,7 +542,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="90">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -885,6 +885,14 @@
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>

--- a/templates/offer_template.xlsx
+++ b/templates/offer_template.xlsx
@@ -1804,15 +1804,15 @@
             </a:tabLst>
           </a:pPr>
           <a:r>
-            <a:rPr lang="de-DE" sz="1100" b="1" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>_________________________                                   _______________________________________</a:t>
+            <a:rPr lang="de-DE" sz="1100" b="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uFillTx/>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:t>_______________________                                   _____________________________________</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="de-DE" sz="1100" b="0" u="none" strike="noStrike">
@@ -1852,43 +1852,6 @@
             <a:t>Datum, Unterschrift Kunde                                          Datum, Unterschrift Umzugsunternehmen</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="900" b="0" u="none" strike="noStrike">
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Times New Roman"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr defTabSz="914400">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:tabLst>
-              <a:tab algn="l" pos="0"/>
-            </a:tabLst>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="de-DE" sz="1100" b="1" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>___________________________________________________________________________</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="de-DE" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" u="none" strike="noStrike">
             <a:effectLst/>
             <a:uFillTx/>
             <a:latin typeface="Times New Roman"/>

--- a/templates/offer_template.xlsx
+++ b/templates/offer_template.xlsx
@@ -1812,7 +1812,7 @@
               <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
-            <a:t>_______________________                                   _____________________________________</a:t>
+            <a:t>_______________________                       ____________________________</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="de-DE" sz="1100" b="0" u="none" strike="noStrike">
@@ -2161,7 +2161,7 @@
               <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
-            <a:t>_______________________                                   _____________________________________ </a:t>
+            <a:t>_______________________                       ____________________________ </a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1100" b="0" u="none" strike="noStrike">
             <a:effectLst/>

--- a/templates/offer_template.xlsx
+++ b/templates/offer_template.xlsx
@@ -2221,7 +2221,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>169284</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2500000" cy="1653578"/>
+    <xdr:ext cx="2000000" cy="1322862"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Grafik 2"/>
@@ -2234,7 +2234,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5200560" y="371520"/>
-          <a:ext cx="2500000" cy="1653578"/>
+          <a:ext cx="2000000" cy="1322862"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
